--- a/DataGrouping/ResultGrouping/hasil_klasifikasi_model_ringkas6_Ryan.xlsx
+++ b/DataGrouping/ResultGrouping/hasil_klasifikasi_model_ringkas6_Ryan.xlsx
@@ -19,17 +19,27 @@
     <sheet name="10_Balance_Terburuk" sheetId="10" r:id="rId10"/>
     <sheet name="10_PCA_Terbaik" sheetId="11" r:id="rId11"/>
     <sheet name="10_PCA_Terburuk" sheetId="12" r:id="rId12"/>
-    <sheet name="10_Normalisasi_Terbaik" sheetId="13" r:id="rId13"/>
-    <sheet name="10_Normalisasi_Terburuk" sheetId="14" r:id="rId14"/>
-    <sheet name="20_Terbaik_No_KFold" sheetId="15" r:id="rId15"/>
-    <sheet name="20_Terburuk_No_KFold" sheetId="16" r:id="rId16"/>
+    <sheet name="10_Norm_Terbaik" sheetId="13" r:id="rId13"/>
+    <sheet name="10_Norm_Terburuk" sheetId="14" r:id="rId14"/>
+    <sheet name="20_Terbaik_NoKFold" sheetId="15" r:id="rId15"/>
+    <sheet name="20_Terburuk_NoKFold" sheetId="16" r:id="rId16"/>
+    <sheet name="PCA_Terbaik_NoKFold" sheetId="17" r:id="rId17"/>
+    <sheet name="PCA_Terburuk_NoKFold" sheetId="18" r:id="rId18"/>
+    <sheet name="Balance_Terbaik_NoKFold" sheetId="19" r:id="rId19"/>
+    <sheet name="Balance_Terburuk_NoKFold" sheetId="20" r:id="rId20"/>
+    <sheet name="Norm_Terbaik_NoKFold" sheetId="21" r:id="rId21"/>
+    <sheet name="Norm_Terburuk_NoKFold" sheetId="22" r:id="rId22"/>
+    <sheet name="ANN_Terbaik_NoKFold" sheetId="23" r:id="rId23"/>
+    <sheet name="ANN_Terburuk_NoKFold" sheetId="24" r:id="rId24"/>
+    <sheet name="Ensemble_Terbaik_NoKFold" sheetId="25" r:id="rId25"/>
+    <sheet name="Ensemble_Terburuk_NoKFold" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="93">
   <si>
     <t>Percobaan</t>
   </si>
@@ -4193,6 +4203,1002 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.968</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.963</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.962</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.967</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.963</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.962</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.966</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.964</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.966</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.964</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.965</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.963</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.958</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.965</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.958</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.959</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.965</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.959</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.963</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.962</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.953</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.963</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.961</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.953</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.962</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.956</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.957</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.455</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.293</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.453</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.414</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.302</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.275</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.317</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.303</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.446</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.336</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.316</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.476</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.488</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.326</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.318</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.442</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.366</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.352</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.387</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.394</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.421</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.377</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.388</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.394</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.423</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.397</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.425</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.479</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.461</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.386</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.384</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I21"/>
@@ -4807,6 +5813,2330 @@
         <v>32</v>
       </c>
       <c r="I21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.406</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.357</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.406</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.357</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.383</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.393</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.408</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.359</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.383</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.393</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.408</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.359</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.383</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.395</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.383</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.395</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.387</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.394</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.421</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.377</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.388</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.394</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.423</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.397</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.425</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.416</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.423</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.392</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.455</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.293</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.453</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.414</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.302</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.275</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.317</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.303</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.446</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.336</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.316</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.476</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.488</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.326</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.318</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.483</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.362</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.337</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.357</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.345</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.442</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.366</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.352</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.381</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.406</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.357</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.383</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.393</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.408</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.359</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.878</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.859</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.862</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.849</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.869</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.855</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.868</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.836</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.849</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.862</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.843</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.862</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.847</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.852</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.829</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.857</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.838</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.861</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.861</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.821</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.837</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.838</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.803</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.785</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.788</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.831</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.759</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.786</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.783</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.798</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.772</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.669</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.703</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.733</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.742</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.659</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.715</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.701</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.707</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.728</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.718</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.746</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.717</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.763</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.742</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.779</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.792</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.803</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.735</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.773</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.764</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.785</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.761</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.768</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.791</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.768</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.781</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.761</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.799</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.783</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.798</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.772</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.986</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.985</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.983</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.981</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.984</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.982</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.979</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="8" width="25.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.455</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0.293</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.453</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.414</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.302</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.275</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.317</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.303</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.476</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.488</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.326</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.318</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.483</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.362</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.337</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.483</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.378</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.362</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.337</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.391</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.416</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.423</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.392</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.403</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.406</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.418</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.396</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.409</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.413</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0.431</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0.397</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.415</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.411</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.436</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.407</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" t="s">
         <v>35</v>
       </c>
     </row>
